--- a/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
@@ -539,10 +539,10 @@
         <v>92</v>
       </c>
       <c r="G10" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H10" t="n">
-        <v>11.96</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H11" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.88</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>16.47</v>
+        <v>12.81</v>
       </c>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="24">
@@ -795,7 +795,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>16.63</v>
+        <v>12.94</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
@@ -522,7 +522,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-MORT-CONTRA</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -532,43 +532,43 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mortero de cemento y arena para contrapiso y capas de nivelación de piso.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09</v>
+        <v>0.225</v>
       </c>
       <c r="H10" t="n">
-        <v>8.279999999999999</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-CEMENTO</t>
+          <t>MT-ARENA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Cemento Portland gris tipo I, en saco.</t>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.225</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="12">
@@ -584,17 +584,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Agua para amasado, humectación de rellenos y compactación.</t>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.025</v>
+        <v>0.0434</v>
       </c>
       <c r="G12" t="n">
         <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9.220000000000001</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>12.81</v>
+        <v>11.87</v>
       </c>
       <c r="H23" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="24">
@@ -795,7 +795,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>12.94</v>
+        <v>11.99</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bases, contrapisos y nivelación</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-040.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Subcapítulo: Bases, contrapisos y nivelación</t>
+          <t>Subcapítulo: Bases, afirmados y nivelación</t>
         </is>
       </c>
     </row>
